--- a/important_mails_2026-04-19.xlsx
+++ b/important_mails_2026-04-19.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,12 +500,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
+          <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
+          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -515,6 +515,53 @@
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
+We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
+Here is a sample of your suppressed ASINs:
+B0FCDRNTT8, B0FD8VC559, B0D7SKQ6GC, B0D97JS8WD
+You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
+https://sellercentral.amazon.com/fixyourproducts/drafts
+To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
+https://sellercentral.amazon.com/performance/account/health/compliance-request
+If you need further help, please raise a case via contact us. - htt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Action Required: Website Suppressed ASINs</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -530,39 +577,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -582,39 +629,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -631,39 +678,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -675,39 +722,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -730,39 +777,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -786,39 +833,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -837,39 +884,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -885,39 +932,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -929,39 +976,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -978,56 +1025,6 @@
 Was this email helpful?
  https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_PRODUCT_REMOVAL_ORDER_CREATED
 SPC-USAmazon-862019321040611</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
         </is>
       </c>
     </row>
@@ -2532,22 +2529,72 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -2565,39 +2612,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -2617,39 +2664,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -2670,39 +2717,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -2723,40 +2770,40 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -2772,39 +2819,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -2827,39 +2874,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2877,39 +2924,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2927,39 +2974,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -2979,39 +3026,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3029,39 +3076,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3079,39 +3126,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3129,39 +3176,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -3176,39 +3223,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3226,39 +3273,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3276,39 +3323,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3326,39 +3373,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3373,39 +3420,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3420,39 +3467,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3467,39 +3514,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3518,40 +3565,40 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3570,39 +3617,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3612,39 +3659,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3662,39 +3709,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3710,40 +3757,40 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -3761,39 +3808,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -3826,39 +3873,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -3873,39 +3920,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -3924,39 +3971,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -3975,39 +4022,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -4019,39 +4066,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -4067,39 +4114,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -4111,39 +4158,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4158,39 +4205,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4202,39 +4249,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4246,39 +4293,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4290,39 +4337,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4334,39 +4381,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4378,39 +4425,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4422,39 +4469,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4466,39 +4513,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4510,39 +4557,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4554,39 +4601,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4605,39 +4652,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4649,39 +4696,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4693,39 +4740,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4737,39 +4784,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4781,39 +4828,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4825,39 +4872,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4869,39 +4916,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4913,39 +4960,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4964,39 +5011,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5008,40 +5055,40 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5060,39 +5107,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5104,39 +5151,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5155,39 +5202,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -5219,39 +5266,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -5278,39 +5325,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -5322,39 +5369,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -5364,39 +5411,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -5406,39 +5453,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -5468,39 +5515,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -5518,39 +5565,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5567,39 +5614,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5615,39 +5662,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -5676,39 +5723,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -5729,39 +5776,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5776,39 +5823,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5822,40 +5869,40 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5871,39 +5918,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5919,39 +5966,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5967,39 +6014,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6015,40 +6062,40 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6064,39 +6111,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6114,39 +6161,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -6162,39 +6209,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6209,39 +6256,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -6256,39 +6303,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6309,40 +6356,40 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -6357,39 +6404,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -6410,39 +6457,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -6475,39 +6522,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6523,39 +6570,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -6568,39 +6615,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6621,39 +6668,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6676,39 +6723,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6729,39 +6776,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6785,39 +6832,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6840,39 +6887,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -6888,39 +6935,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -6940,39 +6987,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -6991,39 +7038,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -7032,39 +7079,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7082,39 +7129,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -7144,39 +7191,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7192,39 +7239,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.

--- a/important_mails_2026-04-19.xlsx
+++ b/important_mails_2026-04-19.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>店铺绩效类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,169 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
+          <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
+          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Action Required: Website Suppressed ASINs</t>
+          <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon Services.
+ We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
+ Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your credit card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For more information, see Making a Payment .
+ You can view your payment activity at any time by logging in to your seller account and going to your Payments Report .
+ Thank you for selling on Amazon.
+ Amazon Services
+ Help us improve your experience on selling on Amazon through this brief survey:
+ https://amazonexteu.qualtrics.com/jfe/form/SV_eUKdboEQhg1YpuK?cID=10038096056-202604191349
+ Was this email helpful?
+ SPC-USAmazon-422214670678490</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Twoja płatność jest już w drodze</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+Ten tytuł będzie wyświetlany na urządzeniach mobilnych
+ Gratulujemy! Twoja płatność jest już w drodze, a środki powinny wkrótce do Ciebie dotrzeć.
+ Próba wypłaty środków
+Gratulacje, Weihai EU! Twoja płatność jest już w drodze, a środki powinny do Ciebie dotrzeć w terminie od trzech do pięciu dni.
+Dnia 04/19/26 14:45 CEST zainicjowaliśmy przelew na kwotę PLN
+ 264.75 na konto powiązane z Twoją metodą płatności (rachunek bankowy o ostatnich cyfrach 229).
+ Jeśli kwota jest mniejsza niż oczekiwana, oto kilka kwestii do wzięcia pod uwagę:
+ Czy Twoje saldo jest niedostępne? Amazon może zatrzymać środki na pokrycie ewentualnych kosztów zwrotów towarów, roszczeń i obciążeń zwrotnych od kupujących. W takim przypadku saldo zamknięcia w raporcie płatności pokaże niedostępne saldo na zarezerwowaną w tym celu kwotę.
+ Czy Twoja sprzedaż wystarczyła na pokrycie wszystkich opłat i zwrotów w tym okresie rozliczeniowym? Kwota płatności uwzględnia koszt działań sprzedażowych, opłaty za sprzedaż oraz opłaty za promocje i usługi. Aby lepiej zrozumieć wysokość salda zamknięcia, warto przeanalizować raport płatności, który znajdziesz w Seller Central w karcie „Raporty”.
+Więcej o raportach płatności w S</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 04/19/26 14:44 BST, we initiated a transfer to your payment method (bank account ending in 191) in the amount of £
+ 220.41.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To find out more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Action Required: Website Suppressed ASINs</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -529,39 +677,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -577,39 +725,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -629,39 +777,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -678,39 +826,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -722,39 +870,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -777,39 +925,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -833,39 +981,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -884,39 +1032,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -932,39 +1080,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -976,39 +1124,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -1028,39 +1176,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1075,39 +1223,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -1124,39 +1272,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1170,39 +1318,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -1221,40 +1369,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -1268,39 +1416,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1322,39 +1470,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1377,39 +1525,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1430,39 +1578,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1485,39 +1633,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -1526,39 +1674,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -1574,39 +1722,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1632,39 +1780,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1685,39 +1833,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1743,39 +1891,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1795,40 +1943,40 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -1844,39 +1992,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1896,39 +2044,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1954,39 +2102,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2002,39 +2150,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2055,39 +2203,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2111,39 +2259,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -2158,39 +2306,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2204,40 +2352,40 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -2254,39 +2402,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2306,39 +2454,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2355,39 +2503,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -2410,39 +2558,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2462,39 +2610,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2511,39 +2659,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2561,40 +2709,40 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -2612,39 +2760,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -2664,39 +2812,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -2717,39 +2865,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -2770,40 +2918,40 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -2819,39 +2967,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -2874,39 +3022,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2924,39 +3072,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2974,39 +3122,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3026,39 +3174,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3076,39 +3224,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3126,39 +3274,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3176,39 +3324,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -3223,39 +3371,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3273,39 +3421,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3323,39 +3471,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3373,39 +3521,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3420,39 +3568,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3467,39 +3615,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3514,39 +3662,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3565,40 +3713,40 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3617,39 +3765,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3659,39 +3807,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3709,39 +3857,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3757,40 +3905,40 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -3808,39 +3956,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -3873,39 +4021,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -3920,39 +4068,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -3971,39 +4119,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -4022,39 +4170,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -4066,39 +4214,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -4114,39 +4262,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -4158,39 +4306,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4205,39 +4353,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4249,39 +4397,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4293,39 +4441,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4337,39 +4485,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4381,39 +4529,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4425,39 +4573,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4469,39 +4617,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4513,39 +4661,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4557,39 +4705,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4601,39 +4749,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4652,39 +4800,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4696,39 +4844,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4740,39 +4888,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4784,39 +4932,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4828,39 +4976,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4872,39 +5020,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4916,39 +5064,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4960,39 +5108,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5011,39 +5159,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5055,40 +5203,40 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5107,39 +5255,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5151,39 +5299,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5202,39 +5350,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -5266,39 +5414,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -5325,39 +5473,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -5369,39 +5517,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -5411,39 +5559,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -5453,39 +5601,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -5515,39 +5663,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -5565,39 +5713,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5614,39 +5762,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5662,39 +5810,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -5723,39 +5871,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -5776,39 +5924,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5823,39 +5971,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5869,40 +6017,40 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5918,39 +6066,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5966,39 +6114,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6014,39 +6162,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6062,40 +6210,40 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6111,39 +6259,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6161,39 +6309,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -6209,39 +6357,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6256,39 +6404,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -6303,39 +6451,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6356,40 +6504,40 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -6404,39 +6552,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -6457,39 +6605,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -6522,87 +6670,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
-Dear there,
-Thank you for being a valued member of the Amazon Multichannel Fulfillment (MCF) and Buy with Prime community. We are reaching again out to make sure you have seen that starting in April 2026, MCF and Buy with Prime will introduce two updates to how orders are packaged and shipped in the United States:
-Packing slips will no longer be included by default.
-Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
-In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
-https://www2.amazonsupplychain.com/e/949422/ence-external-GVCFXDFYNCTFLTTQ/61b9cx/1372255659/h/xX050fPuJyuSx_HuFPheaHfGRXD19yafaiWekQ5-4Gg
-Packing slips will no longer be included by default.
-Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
-In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
-These updates support Amazon’s co</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -6615,39 +6715,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6668,39 +6768,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6723,119 +6823,10 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-02</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-04-02 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: X002A05YW5 Quantity: 1
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- kpCypnMqWe
- Unsellable Products:
-- FNSKU: X00265F4H9 Quantity: 1
-- FNSKU: X002C17O8J Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferen</t>
-        </is>
-      </c>
-    </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>货件/库存类</t>
+          <t>其他风险类</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6850,76 +6841,21 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
+          <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
+          <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- AJ3wMIfu1v
- Unsellable Products:
-- FNSKU: X002A05YW5 Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -6935,39 +6871,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -6987,39 +6923,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -7038,39 +6974,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -7079,39 +7015,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7129,39 +7065,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -7191,39 +7127,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7239,39 +7175,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
